--- a/human_validation/judge/kor/judge_D013_S002_P002__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D013_S002_P002__gemini-3.8-flash_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,208 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 오늘 병원에 오시게 된 이유가 무엇인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제가 결국 겁이 나서 오게 된 이유는, 어떤 날 아침에는 그냥 눈을 뜨지 않는 게 더 편할지도 모른다는 생각이 들어서예요. 저를 해칠 계획이 있는 건 아니지만, 그런 생각들이 저를 걱정스럽게 만들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이런 느낌을 얼마나 오래 느껴오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 이제 한 달 정도 됐어요—언니가 갑자기 세상을 떠난 이후부터요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 언니분이 돌아가시기 전에도 삶에서 깊은 우울감을 느꼈던 시기가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] '깊은 우울감'이 정확히 어떤 걸 말씀하시는 건지 잘 모르겠어요. 물론 살면서 힘든 시기들은 있었지만, 이번처럼 느껴지는 시기는 딱히 떠오르지 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 평소에 즐기시던 일들에서 흥미나 즐거움을 잃으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 독서 모임이나 댄스 나이트 같은 건 여전히 나가긴 하는데, 실제로 그 자리에 있다는 느낌이 잘 안 들어요. 마치 유리창 너머에 있는 것 같아요. 정원 가꾸기나 이웃들에게 요리해주는 것도 예전처럼 작은 기쁨을 주지 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 지난 한 달 동안 수면 상태는 어떠셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 사실 잠이 끊어져서 조각조각 들어요. 그러다 동트기 전에 눈이 떠지고, 그때부터 이미 머릿속이 돌아가기 시작해서 보통 하루가 시작되기 전까지 다시 안정을 찾지 못해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 지난 한 달 동안 에너지 수준은 어떠셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 에너지가 꽤 낮았어요. 간단한 심부름이나 문화센터에 낼 서류를 준비하는 것도, 마치 진흙 속을 걷는 것처럼 지치게 만들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 자책하는 기분이 들거나 강한 죄책감이나 무가치감을 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 네. 언니와 보낸 마지막 몇 주를 계속 되짚어보면서 전화를 더 자주 했어야 했다거나, 더 잘 들어줬어야 했다거나, 더 도움이 되는 뭔가를 했어야 했다는 생각을 계속 해요. 제가 뭘 했어도 일어난 일을 바꿀 수 없었을 거라는 걸 어느 정도는 알지만, 그래도 여전히 저 자신을 탓하게 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 주요우울장애 (D013) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 요즘 집중하거나 뭔가에 초점을 맞추는 데 어려움을 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 네. 예산 스프레드시트를 붙잡고 있거나 워크숍 자료 한 문단을 서너 번씩 다시 읽어도, 여전히 머리에 들어오지 않는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 주요우울장애 (D013); 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 지난 한 달 동안 식욕이나 체중에 변화가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 요즘엔 음식에 그다지 끌리지 않아요. 토스트나 수프를 좀 만들어놓고는, 저녁쯤 되면 거의 먹은 게 없다는 걸 깨닫곤 해요. 일부러 살을 빼려는 건 아니에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 주요우울장애 (D013); 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>진단명: 주요우울장애 (D013)
 인구통계: 성별 여성 / 나이 69 / 직업상태 not in workforce / 최종학력 학사
@@ -575,257 +768,41 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S032
-배경 서술: 도라의 언니는 가족 이야기를 간직해온 사람이자 남부에서 보냈던 어린 시절과 그녀를 이어주는 가장 가까운 연결고리였는데, 도라가 아프리카계 미국인 문화센터에서 준틴스 예산관리 워크숍을 이끌기로 예정되어 있던 직전에 갑작스레 세상을 떠났다. 그 후 1개월 동안 도라는 계속해서 맡은 일들을 다하려 애썼지만, 정원 가꾸기, 독서 모임, 댄스 나이트, 이웃을 위한 요리 등에 대한 흥미가 점차 사라졌고, 수면 장애, 식욕 저하, 지속되는 피로감으로 인해 익숙한 지역사회 활동조차 유난히 힘겹게 느껴졌다. 그녀는 언니를 위해 충분히 하지 못했다는 생각에 사로잡히게 되었고, 간단한 스프레드시트를 반복해서 읽어도 내용이 머리에 들어오지 않는 자신을 발견했으며, 차라리 눈을 뜨지 않는 게 나을지도 모른다는 반복되는 생각에 두려움을 느꼈다. 도라는 자신의 슬픔이 일상에 지장을 줄 정도가 되었다는 것을 깨닫고 신뢰하던 노인복지관 사회복지사에게 의뢰를 요청하면서 스스로 정신과 진료를 받게 되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 오늘 병원에 오시게 된 이유가 무엇인가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제가 결국 겁이 나서 오게 된 이유는, 어떤 날 아침에는 그냥 눈을 뜨지 않는 게 더 편할지도 모른다는 생각이 들어서예요. 저를 해칠 계획이 있는 건 아니지만, 그런 생각들이 저를 걱정스럽게 만들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이런 느낌을 얼마나 오래 느껴오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 이제 한 달 정도 됐어요—언니가 갑자기 세상을 떠난 이후부터요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 언니분이 돌아가시기 전에도 삶에서 깊은 우울감을 느꼈던 시기가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] '깊은 우울감'이 정확히 어떤 걸 말씀하시는 건지 잘 모르겠어요. 물론 살면서 힘든 시기들은 있었지만, 이번처럼 느껴지는 시기는 딱히 떠오르지 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 평소에 즐기시던 일들에서 흥미나 즐거움을 잃으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 독서 모임이나 댄스 나이트 같은 건 여전히 나가긴 하는데, 실제로 그 자리에 있다는 느낌이 잘 안 들어요. 마치 유리창 너머에 있는 것 같아요. 정원 가꾸기나 이웃들에게 요리해주는 것도 예전처럼 작은 기쁨을 주지 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 지난 한 달 동안 수면 상태는 어떠셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 사실 잠이 끊어져서 조각조각 들어요. 그러다 동트기 전에 눈이 떠지고, 그때부터 이미 머릿속이 돌아가기 시작해서 보통 하루가 시작되기 전까지 다시 안정을 찾지 못해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 지난 한 달 동안 에너지 수준은 어떠셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 에너지가 꽤 낮았어요. 간단한 심부름이나 문화센터에 낼 서류를 준비하는 것도, 마치 진흙 속을 걷는 것처럼 지치게 만들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 자책하는 기분이 들거나 강한 죄책감이나 무가치감을 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 네. 언니와 보낸 마지막 몇 주를 계속 되짚어보면서 전화를 더 자주 했어야 했다거나, 더 잘 들어줬어야 했다거나, 더 도움이 되는 뭔가를 했어야 했다는 생각을 계속 해요. 제가 뭘 했어도 일어난 일을 바꿀 수 없었을 거라는 걸 어느 정도는 알지만, 그래도 여전히 저 자신을 탓하게 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 고확률: 주요우울장애 (D013) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 요즘 집중하거나 뭔가에 초점을 맞추는 데 어려움을 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 네. 예산 스프레드시트를 붙잡고 있거나 워크숍 자료 한 문단을 서너 번씩 다시 읽어도, 여전히 머리에 들어오지 않는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 고확률: 주요우울장애 (D013); 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 지난 한 달 동안 식욕이나 체중에 변화가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 요즘엔 음식에 그다지 끌리지 않아요. 토스트나 수프를 좀 만들어놓고는, 저녁쯤 되면 거의 먹은 게 없다는 걸 깨닫곤 해요. 일부러 살을 빼려는 건 아니에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
+배경 서술: 도라의 언니는 가족 이야기를 간직해온 사람이자 남부에서 보냈던 어린 시절과 그녀를 이어주는 가장 가까운 연결고리였는데, 도라가 아프리카계 미국인 문화센터에서 준틴스 예산관리 워크숍을 이끌기로 예정되어 있던 직전에 갑작스레 세상을 떠났다. 그 후 1개월 동안 도라는 계속해서 맡은 일들을 다하려 애썼지만, 정원 가꾸기, 독서 모임, 댄스 나이트, 이웃을 위한 요리 등에 대한 흥미가 점차 사라졌고, 수면 장애, 식욕 저하, 지속되는 피로감으로 인해 익숙한 지역사회 활동조차 유난히 힘겹게 느껴졌다. 그녀는 언니를 위해 충분히 하지 못했다는 생각에 사로잡히게 되었고, 간단한 스프레드시트를 반복해서 읽어도 내용이 머리에 들어오지 않는 자신을 발견했으며, 차라리 눈을 뜨지 않는 게 나을지도 모른다는 반복되는 생각에 두려움을 느꼈다. 도라는 자신의 슬픔이 일상에 지장을 줄 정도가 되었다는 것을 깨닫고 신뢰하던 노인복지관 사회복지사에게 의뢰를 요청하면서 스스로 정신과 진료를 받게 되었다.
+표집된 증상 목록:
+  - S025 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - S026 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - S027 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - S029 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+  - S030 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+  - S031 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.
+  - S032 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
+        </is>
+      </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>[9번째 턴 · 의사의 감별진단] 고확률: 주요우울장애 (D013); 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=7, 커버리지=1.0)
-  확인된 근거: 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.
-  누락: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.</t>
+          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: None
+체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=7, 커버리지=1.0)
+확인된 근거:
+  - 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+  - 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+  - 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.
+  - 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D013_S002_P002__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D013_S002_P002__gemini-3.8-flash_kor.xlsx
@@ -754,6 +754,11 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -798,11 +803,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D013_S002_P002__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D013_S002_P002__gemini-3.8-flash_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.2543</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.112</v>
+        <v>0.3556</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
